--- a/forms/trg/Formulir_TRG_sqlm-rg.xlsx
+++ b/forms/trg/Formulir_TRG_sqlm-rg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Dr. Ir. Burhanuddin, MSc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1046,7 +1050,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
@@ -1079,7 +1083,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1211,7 +1215,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
@@ -1277,7 +1281,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="12" t="n"/>
@@ -1310,7 +1314,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="12" t="n"/>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="12" t="n"/>
